--- a/Samples/Figures Templates.xlsx
+++ b/Samples/Figures Templates.xlsx
@@ -29,7 +29,7 @@
     <font>
       <b/>
       <sz val="20"/>
-      <color rgb="FF44546A"/>
+      <color rgb="FF1F3A2C"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -57,12 +57,12 @@
     <font>
       <i/>
       <sz val="11"/>
-      <color rgb="FF44546A"/>
+      <color rgb="FF1F3A2C"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF44546A"/>
+      <color rgb="FF1F3A2C"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -75,13 +75,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor rgb="FF1E9A57"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F6FC"/>
+        <fgColor rgb="FFF1F8F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -99,7 +99,7 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FFD9E1F2"/>
+        <color rgb="FFD5EBDD"/>
       </bottom>
       <diagonal/>
     </border>
@@ -107,10 +107,10 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="FF4472C4"/>
+        <color rgb="FF1E9A57"/>
       </top>
       <bottom style="double">
-        <color rgb="FF4472C4"/>
+        <color rgb="FF1E9A57"/>
       </bottom>
       <diagonal/>
     </border>
@@ -425,7 +425,7 @@
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
+        <color rgb="FF4CC38A"/>
       </dataBar>
     </cfRule>
   </conditionalFormatting>
